--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_02-05-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_02-05-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E84F1AE6-742D-4072-8672-2838C7278BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BAE8732-D83F-4DEC-AED0-EDBA267899DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
